--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnas\Desktop\baigiamasis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB928D67-DE66-471C-B834-6FD13A9230D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731F5A32-980B-4D05-A5A3-29247C281E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPI" sheetId="1" r:id="rId1"/>
@@ -15693,7 +15693,7 @@
         <v>0.5</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F24" t="s">
         <v>842</v>
@@ -15707,13 +15707,13 @@
         <v>508</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F25" t="s">
         <v>842</v>
@@ -15727,13 +15727,13 @@
         <v>102</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F26" t="s">
         <v>842</v>
@@ -15747,13 +15747,13 @@
         <v>509</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F27" t="s">
         <v>842</v>
@@ -15767,13 +15767,13 @@
         <v>510</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F28" t="s">
         <v>842</v>
@@ -15787,13 +15787,13 @@
         <v>107</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F29" t="s">
         <v>842</v>
@@ -15807,13 +15807,13 @@
         <v>108</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F30" t="s">
         <v>842</v>
@@ -15827,13 +15827,13 @@
         <v>511</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F31" t="s">
         <v>842</v>
@@ -15847,13 +15847,13 @@
         <v>111</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F32" t="s">
         <v>842</v>
@@ -15867,13 +15867,13 @@
         <v>512</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F33" t="s">
         <v>842</v>
@@ -15887,13 +15887,13 @@
         <v>114</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F34" t="s">
         <v>842</v>
@@ -15907,13 +15907,13 @@
         <v>513</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F35" t="s">
         <v>842</v>
@@ -15927,13 +15927,13 @@
         <v>117</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F36" t="s">
         <v>842</v>
@@ -15947,13 +15947,13 @@
         <v>514</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F37" t="s">
         <v>842</v>
@@ -15967,13 +15967,13 @@
         <v>55</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F38" t="s">
         <v>842</v>
@@ -15987,13 +15987,13 @@
         <v>312</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F39" t="s">
         <v>842</v>
@@ -16007,7 +16007,7 @@
         <v>515</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -18807,13 +18807,13 @@
         <v>518</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F180" t="s">
         <v>842</v>
@@ -18827,13 +18827,13 @@
         <v>316</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F181" t="s">
         <v>842</v>
@@ -18847,13 +18847,13 @@
         <v>598</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F182" t="s">
         <v>842</v>
@@ -18867,13 +18867,13 @@
         <v>272</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F183" t="s">
         <v>842</v>
@@ -18887,13 +18887,13 @@
         <v>599</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F184" t="s">
         <v>842</v>
@@ -18907,13 +18907,13 @@
         <v>600</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F185" t="s">
         <v>842</v>
@@ -18927,7 +18927,7 @@
         <v>75</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D186">
         <v>-0.1</v>
